--- a/exports/trend_1d/INDIGO_full_report.xlsx
+++ b/exports/trend_1d/INDIGO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>20.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42390</v>
+        <v>42391</v>
       </c>
       <c r="H2" t="n">
-        <v>1197.85</v>
+        <v>968.3</v>
       </c>
       <c r="I2" t="n">
         <v>1116.056514650629</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K2" t="n">
-        <v>10.08</v>
+        <v>-11.02</v>
       </c>
       <c r="L2" t="n">
-        <v>9.76</v>
+        <v>11.94</v>
       </c>
       <c r="M2" t="n">
         <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>6.06</v>
+        <v>19.16</v>
       </c>
       <c r="O2" t="n">
         <v>-0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>36.71</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42460</v>
+        <v>42461</v>
       </c>
       <c r="H3" t="n">
-        <v>873.2</v>
+        <v>908.55</v>
       </c>
       <c r="I3" t="n">
         <v>905.7341945268428</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>9.82</v>
+        <v>6.17</v>
       </c>
       <c r="L3" t="n">
         <v>21.35</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H4" t="n">
-        <v>1008.4</v>
+        <v>962.5</v>
       </c>
       <c r="I4" t="n">
         <v>978.0831698621599</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>10.99</v>
+        <v>5.94</v>
       </c>
       <c r="L4" t="n">
         <v>5.12</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>12.69</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42538</v>
+        <v>42541</v>
       </c>
       <c r="H5" t="n">
-        <v>1013.45</v>
+        <v>1071.7</v>
       </c>
       <c r="I5" t="n">
         <v>1070.795262145217</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.29</v>
+        <v>-11.35</v>
       </c>
       <c r="L5" t="n">
-        <v>11.11</v>
+        <v>13.14</v>
       </c>
       <c r="M5" t="n">
         <v>1.19</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
         <v>-4.55</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.83</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42569</v>
+        <v>42570</v>
       </c>
       <c r="H6" t="n">
-        <v>950.3</v>
+        <v>947.1</v>
       </c>
       <c r="I6" t="n">
         <v>949.1492648402839</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.33</v>
+        <v>-11.63</v>
       </c>
       <c r="L6" t="n">
         <v>20.07</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.82</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42601</v>
+        <v>42604</v>
       </c>
       <c r="H7" t="n">
-        <v>880.7</v>
+        <v>901.9</v>
       </c>
       <c r="I7" t="n">
         <v>885.5031773461129</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>7.01</v>
+        <v>4.77</v>
       </c>
       <c r="L7" t="n">
         <v>5.34</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.78</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H8" t="n">
-        <v>883.6</v>
+        <v>833.4</v>
       </c>
       <c r="I8" t="n">
         <v>882.6067211118498</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.03</v>
+        <v>-7.6</v>
       </c>
       <c r="L8" t="n">
         <v>10.57</v>
@@ -897,7 +992,7 @@
         <v>6.69</v>
       </c>
       <c r="N8" t="n">
-        <v>3.46</v>
+        <v>5.68</v>
       </c>
       <c r="O8" t="n">
         <v>2.41</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.65</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H9" t="n">
-        <v>860</v>
+        <v>869.05</v>
       </c>
       <c r="I9" t="n">
         <v>867.0030613329757</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.19</v>
+        <v>-4.28</v>
       </c>
       <c r="L9" t="n">
         <v>11.34</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42766</v>
+        <v>42767</v>
       </c>
       <c r="H10" t="n">
-        <v>903</v>
+        <v>836.55</v>
       </c>
       <c r="I10" t="n">
         <v>875.2064219333378</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>3.91</v>
+        <v>-3.74</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>5.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.55</v>
+        <v>5.87</v>
       </c>
       <c r="N10" t="n">
-        <v>3.44</v>
+        <v>7.36</v>
       </c>
       <c r="O10" t="n">
         <v>1.05</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.59</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42801</v>
+        <v>42802</v>
       </c>
       <c r="H11" t="n">
-        <v>860.1</v>
+        <v>879.8</v>
       </c>
       <c r="I11" t="n">
         <v>877.4757881505867</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.82</v>
+        <v>-5.17</v>
       </c>
       <c r="L11" t="n">
-        <v>6.27</v>
+        <v>7.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42970</v>
+        <v>42971</v>
       </c>
       <c r="H12" t="n">
-        <v>1216.45</v>
+        <v>1186.6</v>
       </c>
       <c r="I12" t="n">
         <v>1199.182426120273</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K12" t="n">
-        <v>38.26</v>
+        <v>34.87</v>
       </c>
       <c r="L12" t="n">
         <v>2.79</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43026</v>
+        <v>43031</v>
       </c>
       <c r="H13" t="n">
-        <v>1149.15</v>
+        <v>1159.6</v>
       </c>
       <c r="I13" t="n">
         <v>1150.613720341989</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>3.16</v>
+        <v>2.28</v>
       </c>
       <c r="L13" t="n">
         <v>7.37</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43068</v>
+        <v>43069</v>
       </c>
       <c r="H14" t="n">
-        <v>1153.5</v>
+        <v>1121.55</v>
       </c>
       <c r="I14" t="n">
         <v>1150.241893231465</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.53</v>
+        <v>-3.28</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>3.8</v>
       </c>
       <c r="M14" t="n">
         <v>0.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="O14" t="n">
         <v>0.91</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H15" t="n">
-        <v>1198.6</v>
+        <v>1225.2</v>
       </c>
       <c r="I15" t="n">
         <v>1223.299146526616</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.87</v>
+        <v>-9.24</v>
       </c>
       <c r="L15" t="n">
         <v>9.57</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43175</v>
+        <v>43178</v>
       </c>
       <c r="H16" t="n">
-        <v>1263.45</v>
+        <v>1215.8</v>
       </c>
       <c r="I16" t="n">
         <v>1223.11222934809</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>3.12</v>
+        <v>-0.77</v>
       </c>
       <c r="L16" t="n">
         <v>6.55</v>
@@ -1353,7 +1544,7 @@
         <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="O16" t="n">
         <v>2.22</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>12.93</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H17" t="n">
-        <v>1328.7</v>
+        <v>1367.85</v>
       </c>
       <c r="I17" t="n">
         <v>1362.381814720745</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.289999999999999</v>
+        <v>-12.51</v>
       </c>
       <c r="L17" t="n">
-        <v>9.890000000000001</v>
+        <v>13.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.34</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.17</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43220</v>
+        <v>43222</v>
       </c>
       <c r="H18" t="n">
-        <v>1402.8</v>
+        <v>1342.85</v>
       </c>
       <c r="I18" t="n">
         <v>1371.546789805676</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>2.56</v>
+        <v>-1.83</v>
       </c>
       <c r="L18" t="n">
         <v>3.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>14.05</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43315</v>
+        <v>43318</v>
       </c>
       <c r="H19" t="n">
-        <v>996.15</v>
+        <v>1066.2</v>
       </c>
       <c r="I19" t="n">
         <v>1049.437497158402</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K19" t="n">
-        <v>25.82</v>
+        <v>20.6</v>
       </c>
       <c r="L19" t="n">
         <v>5.21</v>
@@ -1524,7 +1751,7 @@
         <v>3.38</v>
       </c>
       <c r="N19" t="n">
-        <v>4.69</v>
+        <v>7.03</v>
       </c>
       <c r="O19" t="n">
         <v>-4.27</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>16.78</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43340</v>
+        <v>43341</v>
       </c>
       <c r="H20" t="n">
-        <v>1023.9</v>
+        <v>966.8</v>
       </c>
       <c r="I20" t="n">
         <v>971.6176727825593</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.97</v>
+        <v>-9.32</v>
       </c>
       <c r="L20" t="n">
-        <v>7.59</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>1.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>5.58</v>
       </c>
       <c r="O20" t="n">
         <v>7.03</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H21" t="n">
-        <v>888.9</v>
+        <v>925.4</v>
       </c>
       <c r="I21" t="n">
         <v>889.011527910825</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K21" t="n">
-        <v>8.06</v>
+        <v>4.28</v>
       </c>
       <c r="L21" t="n">
         <v>6.43</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>16.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43475</v>
+        <v>43476</v>
       </c>
       <c r="H22" t="n">
-        <v>1097</v>
+        <v>1057.45</v>
       </c>
       <c r="I22" t="n">
         <v>1071.902282395504</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K22" t="n">
-        <v>18.54</v>
+        <v>14.27</v>
       </c>
       <c r="L22" t="n">
         <v>3.92</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H23" t="n">
-        <v>1109.3</v>
+        <v>1178.55</v>
       </c>
       <c r="I23" t="n">
         <v>1163.116939794893</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.9</v>
+        <v>-11.45</v>
       </c>
       <c r="L23" t="n">
-        <v>8.369999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="M23" t="n">
         <v>0.13</v>
       </c>
       <c r="N23" t="n">
-        <v>5.43</v>
+        <v>6.24</v>
       </c>
       <c r="O23" t="n">
         <v>-3.61</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>16.1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H24" t="n">
-        <v>1566.3</v>
+        <v>1398.05</v>
       </c>
       <c r="I24" t="n">
         <v>1540.062310567138</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K24" t="n">
-        <v>32.9</v>
+        <v>18.62</v>
       </c>
       <c r="L24" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>9.029999999999999</v>
+        <v>10.74</v>
       </c>
       <c r="O24" t="n">
         <v>6.24</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.07</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H25" t="n">
-        <v>1523.4</v>
+        <v>1595</v>
       </c>
       <c r="I25" t="n">
         <v>1566.744949406984</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.970000000000001</v>
+        <v>-14.09</v>
       </c>
       <c r="L25" t="n">
-        <v>9.92</v>
+        <v>15.88</v>
       </c>
       <c r="M25" t="n">
         <v>1.31</v>
       </c>
       <c r="N25" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
         <v>-10.74</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>18.88</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43756</v>
+        <v>43760</v>
       </c>
       <c r="H26" t="n">
-        <v>1729.9</v>
+        <v>1674.35</v>
       </c>
       <c r="I26" t="n">
         <v>1705.446911095103</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K26" t="n">
-        <v>8.460000000000001</v>
+        <v>4.97</v>
       </c>
       <c r="L26" t="n">
         <v>11.5</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43839</v>
+        <v>43840</v>
       </c>
       <c r="H27" t="n">
-        <v>1402.2</v>
+        <v>1416.3</v>
       </c>
       <c r="I27" t="n">
         <v>1407.6146696652</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" t="n">
-        <v>16.25</v>
+        <v>15.41</v>
       </c>
       <c r="L27" t="n">
         <v>2.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H28" t="n">
-        <v>1419.2</v>
+        <v>1378.25</v>
       </c>
       <c r="I28" t="n">
         <v>1378.291616274792</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>-2.69</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
         <v>0.84</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.8</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43985</v>
+        <v>43986</v>
       </c>
       <c r="H29" t="n">
-        <v>1023.2</v>
+        <v>1116.05</v>
       </c>
       <c r="I29" t="n">
         <v>1101.86620487171</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K29" t="n">
-        <v>25.76</v>
+        <v>19.02</v>
       </c>
       <c r="L29" t="n">
         <v>8.35</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>21.18</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H30" t="n">
-        <v>1014.85</v>
+        <v>955.3</v>
       </c>
       <c r="I30" t="n">
         <v>962.1340081568717</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>-9.07</v>
+        <v>-14.4</v>
       </c>
       <c r="L30" t="n">
-        <v>14.83</v>
+        <v>15.66</v>
       </c>
       <c r="M30" t="n">
         <v>4.94</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>14.63</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44054</v>
+        <v>44055</v>
       </c>
       <c r="H31" t="n">
-        <v>939.65</v>
+        <v>1034.55</v>
       </c>
       <c r="I31" t="n">
         <v>1011.232571270762</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>1.64</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>5.66</v>
+        <v>10.54</v>
       </c>
       <c r="M31" t="n">
         <v>1.24</v>
       </c>
       <c r="N31" t="n">
-        <v>4.41</v>
+        <v>10.1</v>
       </c>
       <c r="O31" t="n">
         <v>-5.87</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>16.4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44161</v>
+        <v>44162</v>
       </c>
       <c r="H32" t="n">
-        <v>1544.35</v>
+        <v>1514.15</v>
       </c>
       <c r="I32" t="n">
         <v>1519.488790010225</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K32" t="n">
-        <v>49.28</v>
+        <v>46.36</v>
       </c>
       <c r="L32" t="n">
         <v>9.51</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.89</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44168</v>
+        <v>44169</v>
       </c>
       <c r="H33" t="n">
-        <v>1644.05</v>
+        <v>1744.8</v>
       </c>
       <c r="I33" t="n">
         <v>1724.520982423176</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.58</v>
+        <v>-15.23</v>
       </c>
       <c r="L33" t="n">
-        <v>9.18</v>
+        <v>15.71</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>6.13</v>
       </c>
       <c r="O33" t="n">
         <v>-1.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>14.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H34" t="n">
-        <v>1651.05</v>
+        <v>1507</v>
       </c>
       <c r="I34" t="n">
         <v>1571.484637030045</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.37</v>
+        <v>-13.63</v>
       </c>
       <c r="L34" t="n">
-        <v>6.84</v>
+        <v>14.76</v>
       </c>
       <c r="M34" t="n">
-        <v>0.36</v>
+        <v>0.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3.22</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>6.13</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.43</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H35" t="n">
-        <v>1713.5</v>
+        <v>1744.95</v>
       </c>
       <c r="I35" t="n">
         <v>1735.799580665379</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.7</v>
+        <v>-15.79</v>
       </c>
       <c r="L35" t="n">
-        <v>15.39</v>
+        <v>16.19</v>
       </c>
       <c r="M35" t="n">
         <v>0.68</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.12</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H36" t="n">
-        <v>1592.8</v>
+        <v>1547.75</v>
       </c>
       <c r="I36" t="n">
         <v>1587.516363913318</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.720000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="L36" t="n">
-        <v>10.6</v>
+        <v>12.09</v>
       </c>
       <c r="M36" t="n">
-        <v>0.74</v>
+        <v>2.06</v>
       </c>
       <c r="N36" t="n">
         <v>3.33</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.02</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44257</v>
+        <v>44258</v>
       </c>
       <c r="H37" t="n">
-        <v>1691.4</v>
+        <v>1782.6</v>
       </c>
       <c r="I37" t="n">
         <v>1694.880893814601</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.279999999999999</v>
+        <v>-15.17</v>
       </c>
       <c r="L37" t="n">
-        <v>12.67</v>
+        <v>17.84</v>
       </c>
       <c r="M37" t="n">
         <v>3.97</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.11</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44287</v>
+        <v>44291</v>
       </c>
       <c r="H38" t="n">
-        <v>1616.6</v>
+        <v>1552.7</v>
       </c>
       <c r="I38" t="n">
         <v>1577.233209116747</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.31</v>
+        <v>-12.9</v>
       </c>
       <c r="L38" t="n">
-        <v>11.63</v>
+        <v>14.45</v>
       </c>
       <c r="M38" t="n">
         <v>1.77</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.96</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H39" t="n">
-        <v>1703.75</v>
+        <v>1714.7</v>
       </c>
       <c r="I39" t="n">
         <v>1707.205400595358</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.73</v>
+        <v>-10.43</v>
       </c>
       <c r="L39" t="n">
-        <v>10.45</v>
+        <v>11.09</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H40" t="n">
-        <v>1765.9</v>
+        <v>1673.95</v>
       </c>
       <c r="I40" t="n">
         <v>1726.007179548561</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K40" t="n">
-        <v>2.99</v>
+        <v>-2.38</v>
       </c>
       <c r="L40" t="n">
         <v>3.37</v>
@@ -2721,7 +3200,7 @@
         <v>1.88</v>
       </c>
       <c r="N40" t="n">
-        <v>3.13</v>
+        <v>5.21</v>
       </c>
       <c r="O40" t="n">
         <v>0.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44434</v>
+        <v>44435</v>
       </c>
       <c r="H41" t="n">
-        <v>1747.8</v>
+        <v>1776.85</v>
       </c>
       <c r="I41" t="n">
         <v>1763.724319713525</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.41</v>
+        <v>-6.15</v>
       </c>
       <c r="L41" t="n">
-        <v>5.49</v>
+        <v>6.51</v>
       </c>
       <c r="M41" t="n">
         <v>1.38</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.85</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H42" t="n">
-        <v>2021.7</v>
+        <v>1976.05</v>
       </c>
       <c r="I42" t="n">
         <v>1990.567467294036</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>13.78</v>
+        <v>11.21</v>
       </c>
       <c r="L42" t="n">
         <v>2.38</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.23</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H43" t="n">
-        <v>1997.95</v>
+        <v>2175.2</v>
       </c>
       <c r="I43" t="n">
         <v>2172.719148939521</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.11</v>
+        <v>-10.08</v>
       </c>
       <c r="L43" t="n">
-        <v>8.300000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="M43" t="n">
         <v>4.89</v>
       </c>
       <c r="N43" t="n">
-        <v>4.37</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>-2.26</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>21.62</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H44" t="n">
-        <v>2141.75</v>
+        <v>2071.6</v>
       </c>
       <c r="I44" t="n">
         <v>2093.668745639897</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.54</v>
+        <v>-4.76</v>
       </c>
       <c r="L44" t="n">
         <v>14.95</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.26</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H45" t="n">
-        <v>2035.55</v>
+        <v>2089</v>
       </c>
       <c r="I45" t="n">
         <v>2055.623672248172</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>1.74</v>
+        <v>-0.84</v>
       </c>
       <c r="L45" t="n">
         <v>3.3</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H46" t="n">
-        <v>1966.7</v>
+        <v>1862.6</v>
       </c>
       <c r="I46" t="n">
         <v>1959.193224343737</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.85</v>
+        <v>-10.84</v>
       </c>
       <c r="L46" t="n">
-        <v>6.39</v>
+        <v>12.02</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="N46" t="n">
-        <v>4.42</v>
+        <v>5.29</v>
       </c>
       <c r="O46" t="n">
         <v>2.63</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.51</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44596</v>
+        <v>44599</v>
       </c>
       <c r="H47" t="n">
-        <v>1974.35</v>
+        <v>2170.1</v>
       </c>
       <c r="I47" t="n">
         <v>2090.892380805412</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-6</v>
+        <v>-16.51</v>
       </c>
       <c r="L47" t="n">
-        <v>7.65</v>
+        <v>17.42</v>
       </c>
       <c r="M47" t="n">
-        <v>0.61</v>
+        <v>1.55</v>
       </c>
       <c r="N47" t="n">
-        <v>5.07</v>
+        <v>9.91</v>
       </c>
       <c r="O47" t="n">
         <v>-5.29</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>15.57</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H48" t="n">
-        <v>2039.4</v>
+        <v>1830.55</v>
       </c>
       <c r="I48" t="n">
         <v>1989.633011902543</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.02</v>
+        <v>-15.65</v>
       </c>
       <c r="L48" t="n">
-        <v>8.529999999999999</v>
+        <v>17.05</v>
       </c>
       <c r="M48" t="n">
         <v>4.34</v>
       </c>
       <c r="N48" t="n">
-        <v>7.62</v>
+        <v>10.24</v>
       </c>
       <c r="O48" t="n">
         <v>9.91</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>20.8</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H49" t="n">
-        <v>1832.55</v>
+        <v>1899.8</v>
       </c>
       <c r="I49" t="n">
         <v>1889.770322332515</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.11</v>
+        <v>-3.78</v>
       </c>
       <c r="L49" t="n">
         <v>8.6</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>15.21</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H50" t="n">
-        <v>1870.2</v>
+        <v>1791.3</v>
       </c>
       <c r="I50" t="n">
         <v>1838.012228665087</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.56</v>
+        <v>-5.71</v>
       </c>
       <c r="L50" t="n">
         <v>7.24</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H51" t="n">
-        <v>1808.9</v>
+        <v>1838.55</v>
       </c>
       <c r="I51" t="n">
         <v>1825.828673175246</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.98</v>
+        <v>-2.64</v>
       </c>
       <c r="L51" t="n">
         <v>5.23</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>13.32</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H52" t="n">
-        <v>1631.95</v>
+        <v>1549.3</v>
       </c>
       <c r="I52" t="n">
         <v>1627.891819938129</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.24</v>
+        <v>-15.73</v>
       </c>
       <c r="L52" t="n">
-        <v>13.03</v>
+        <v>17.77</v>
       </c>
       <c r="M52" t="n">
         <v>1.58</v>
       </c>
       <c r="N52" t="n">
-        <v>4.97</v>
+        <v>5.06</v>
       </c>
       <c r="O52" t="n">
         <v>1.64</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>16.86</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H53" t="n">
-        <v>1785.85</v>
+        <v>1801.15</v>
       </c>
       <c r="I53" t="n">
         <v>1796.448665026503</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>-15.27</v>
+        <v>-16.26</v>
       </c>
       <c r="L53" t="n">
-        <v>15.54</v>
+        <v>16.76</v>
       </c>
       <c r="M53" t="n">
         <v>2.37</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H54" t="n">
-        <v>1902.1</v>
+        <v>1836.05</v>
       </c>
       <c r="I54" t="n">
         <v>1897.94168831976</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K54" t="n">
-        <v>5.6</v>
+        <v>1.94</v>
       </c>
       <c r="L54" t="n">
         <v>2.75</v>
@@ -3519,7 +4166,7 @@
         <v>2.61</v>
       </c>
       <c r="N54" t="n">
-        <v>2.56</v>
+        <v>3.47</v>
       </c>
       <c r="O54" t="n">
         <v>0.86</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.79</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44887</v>
+        <v>44888</v>
       </c>
       <c r="H55" t="n">
-        <v>1818.95</v>
+        <v>1893.35</v>
       </c>
       <c r="I55" t="n">
         <v>1851.66877402349</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K55" t="n">
-        <v>0.93</v>
+        <v>-3.12</v>
       </c>
       <c r="L55" t="n">
         <v>5.01</v>
@@ -3576,7 +4235,7 @@
         <v>2.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.65</v>
+        <v>4.09</v>
       </c>
       <c r="O55" t="n">
         <v>-3.47</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>9.16</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H56" t="n">
-        <v>1986.05</v>
+        <v>1897.25</v>
       </c>
       <c r="I56" t="n">
         <v>1969.076050134279</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K56" t="n">
-        <v>4.9</v>
+        <v>0.21</v>
       </c>
       <c r="L56" t="n">
         <v>3.57</v>
       </c>
       <c r="M56" t="n">
-        <v>1.51</v>
+        <v>3.22</v>
       </c>
       <c r="N56" t="n">
-        <v>3.18</v>
+        <v>4.47</v>
       </c>
       <c r="O56" t="n">
         <v>4.09</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H57" t="n">
-        <v>1937</v>
+        <v>1960</v>
       </c>
       <c r="I57" t="n">
         <v>1946.534335190584</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.1</v>
+        <v>-3.31</v>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>3.83</v>
       </c>
       <c r="M57" t="n">
         <v>1.46</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.63</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45132</v>
+        <v>45133</v>
       </c>
       <c r="H58" t="n">
-        <v>2584.4</v>
+        <v>2539.85</v>
       </c>
       <c r="I58" t="n">
         <v>2547.940788319727</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K58" t="n">
-        <v>31.86</v>
+        <v>29.58</v>
       </c>
       <c r="L58" t="n">
         <v>1.21</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45204</v>
+        <v>45205</v>
       </c>
       <c r="H59" t="n">
-        <v>2473.4</v>
+        <v>2535.5</v>
       </c>
       <c r="I59" t="n">
         <v>2507.246794923739</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K59" t="n">
-        <v>2.62</v>
+        <v>0.17</v>
       </c>
       <c r="L59" t="n">
         <v>4.34</v>
       </c>
       <c r="M59" t="n">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
         <v>3.71</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.78</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H60" t="n">
-        <v>2439.05</v>
+        <v>2390.95</v>
       </c>
       <c r="I60" t="n">
         <v>2435.813819220552</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.8</v>
+        <v>-5.7</v>
       </c>
       <c r="L60" t="n">
-        <v>4.16</v>
+        <v>5.78</v>
       </c>
       <c r="M60" t="n">
         <v>1.48</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.58</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H61" t="n">
-        <v>2567.2</v>
+        <v>2606.55</v>
       </c>
       <c r="I61" t="n">
         <v>2587.40186587461</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.37</v>
+        <v>-9.02</v>
       </c>
       <c r="L61" t="n">
-        <v>9.119999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="M61" t="n">
         <v>1.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.56</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45315</v>
+        <v>45316</v>
       </c>
       <c r="H62" t="n">
-        <v>2910.15</v>
+        <v>2863.05</v>
       </c>
       <c r="I62" t="n">
         <v>2891.897341156446</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K62" t="n">
-        <v>11.65</v>
+        <v>9.84</v>
       </c>
       <c r="L62" t="n">
         <v>1.7</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>8.82</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="H63" t="n">
-        <v>3066.6</v>
+        <v>3127.1</v>
       </c>
       <c r="I63" t="n">
         <v>3115.216400081345</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.11</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>7.64</v>
+        <v>10.02</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="N63" t="n">
         <v>3.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.09</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45440</v>
+        <v>45441</v>
       </c>
       <c r="H64" t="n">
-        <v>4197.05</v>
+        <v>4027.55</v>
       </c>
       <c r="I64" t="n">
         <v>4054.524530772532</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K64" t="n">
-        <v>34.22</v>
+        <v>28.8</v>
       </c>
       <c r="L64" t="n">
         <v>4.57</v>
@@ -4089,7 +4856,7 @@
         <v>2.37</v>
       </c>
       <c r="N64" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="O64" t="n">
         <v>1.97</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>11.25</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45450</v>
+        <v>45453</v>
       </c>
       <c r="H65" t="n">
-        <v>4373.2</v>
+        <v>4566.6</v>
       </c>
       <c r="I65" t="n">
         <v>4480.649100360142</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.58</v>
+        <v>-13.38</v>
       </c>
       <c r="L65" t="n">
-        <v>9.52</v>
+        <v>14.46</v>
       </c>
       <c r="M65" t="n">
         <v>3.22</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H66" t="n">
-        <v>4716.85</v>
+        <v>4609.35</v>
       </c>
       <c r="I66" t="n">
         <v>4655.01852444322</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K66" t="n">
-        <v>3.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L66" t="n">
         <v>9.119999999999999</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H67" t="n">
-        <v>4229.6</v>
+        <v>4267.9</v>
       </c>
       <c r="I67" t="n">
         <v>4249.184957433019</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K67" t="n">
-        <v>8.24</v>
+        <v>7.41</v>
       </c>
       <c r="L67" t="n">
         <v>3.9</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H68" t="n">
-        <v>4466.2</v>
+        <v>4266.95</v>
       </c>
       <c r="I68" t="n">
         <v>4336.871920971153</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K68" t="n">
-        <v>4.65</v>
+        <v>-0.02</v>
       </c>
       <c r="L68" t="n">
         <v>2.27</v>
@@ -4317,7 +5132,7 @@
         <v>3.08</v>
       </c>
       <c r="N68" t="n">
-        <v>1.8</v>
+        <v>4.46</v>
       </c>
       <c r="O68" t="n">
         <v>0.91</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>11.07</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H69" t="n">
-        <v>4324.35</v>
+        <v>4492.4</v>
       </c>
       <c r="I69" t="n">
         <v>4369.050025594288</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.35</v>
+        <v>-5.28</v>
       </c>
       <c r="L69" t="n">
-        <v>5.08</v>
+        <v>5.86</v>
       </c>
       <c r="M69" t="n">
         <v>1.47</v>
       </c>
       <c r="N69" t="n">
-        <v>3.07</v>
+        <v>3.89</v>
       </c>
       <c r="O69" t="n">
         <v>-4.46</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.58</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H70" t="n">
-        <v>5727</v>
+        <v>5646</v>
       </c>
       <c r="I70" t="n">
         <v>5726.688652613031</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K70" t="n">
-        <v>27.48</v>
+        <v>25.68</v>
       </c>
       <c r="L70" t="n">
         <v>7.45</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>8</v>
+      </c>
+      <c r="U70" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>8.15</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="H71" t="n">
-        <v>5848</v>
+        <v>5934</v>
       </c>
       <c r="I71" t="n">
         <v>5912.929066721982</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.58</v>
+        <v>-5.1</v>
       </c>
       <c r="L71" t="n">
-        <v>5.04</v>
+        <v>5.28</v>
       </c>
       <c r="M71" t="n">
         <v>0.74</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>5.33</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H72" t="n">
-        <v>5725</v>
+        <v>5625</v>
       </c>
       <c r="I72" t="n">
         <v>5649.898914946109</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.52</v>
+        <v>-5.21</v>
       </c>
       <c r="L72" t="n">
-        <v>4.04</v>
+        <v>5.59</v>
       </c>
       <c r="M72" t="n">
         <v>0.48</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.25</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H73" t="n">
-        <v>4960.4</v>
+        <v>5013.8</v>
       </c>
       <c r="I73" t="n">
         <v>4974.102109476921</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K73" t="n">
-        <v>11.82</v>
+        <v>10.87</v>
       </c>
       <c r="L73" t="n">
         <v>6.13</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.56</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H74" t="n">
-        <v>4827.2</v>
+        <v>4520.4</v>
       </c>
       <c r="I74" t="n">
         <v>4679.949385710839</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.72</v>
+        <v>-9.84</v>
       </c>
       <c r="L74" t="n">
-        <v>4.59</v>
+        <v>10.25</v>
       </c>
       <c r="M74" t="n">
-        <v>1.03</v>
+        <v>6.78</v>
       </c>
       <c r="N74" t="n">
-        <v>3.32</v>
+        <v>6.36</v>
       </c>
       <c r="O74" t="n">
         <v>1.08</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>9.65</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H75" t="n">
-        <v>4268.8</v>
+        <v>4615.5</v>
       </c>
       <c r="I75" t="n">
         <v>4503.805519833934</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K75" t="n">
-        <v>5.57</v>
+        <v>-2.1</v>
       </c>
       <c r="L75" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="M75" t="n">
-        <v>4.09</v>
+        <v>7.76</v>
       </c>
       <c r="N75" t="n">
-        <v>6.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O75" t="n">
         <v>-6.36</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>13.87</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H76" t="n">
-        <v>5117</v>
+        <v>5023.5</v>
       </c>
       <c r="I76" t="n">
         <v>5059.771388994217</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K76" t="n">
-        <v>10.87</v>
+        <v>8.84</v>
       </c>
       <c r="L76" t="n">
         <v>10.17</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>8.84</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H77" t="n">
-        <v>5171</v>
+        <v>5400</v>
       </c>
       <c r="I77" t="n">
         <v>5361.349498928803</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.94</v>
+        <v>-7.49</v>
       </c>
       <c r="L77" t="n">
-        <v>5.5</v>
+        <v>7.53</v>
       </c>
       <c r="M77" t="n">
         <v>2.53</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="H78" t="n">
-        <v>5020</v>
+        <v>4980</v>
       </c>
       <c r="I78" t="n">
         <v>5010.89166811122</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.04</v>
+        <v>-7.78</v>
       </c>
       <c r="L78" t="n">
         <v>9.1</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>37</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9565,7 +10520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="6">
@@ -9575,7 +10530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -9585,7 +10540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -9595,7 +10550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9605,7 +10560,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -9615,7 +10570,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.2</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="11">
@@ -9625,7 +10580,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -9635,7 +10590,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9645,7 +10600,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.6</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="14">
@@ -9655,7 +10610,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.86</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="15">
@@ -9665,7 +10620,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.02</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="16">
@@ -9675,7 +10630,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="17">
@@ -9685,7 +10640,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.28</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="18">
@@ -9695,7 +10650,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="19">
@@ -9705,7 +10660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.34</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9715,7 +10670,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.84</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="21">
@@ -9735,7 +10690,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -9745,7 +10700,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -9755,7 +10710,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="25">
@@ -9765,7 +10720,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9775,7 +10730,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.54</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="27">
@@ -9785,7 +10740,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.36</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="28">
@@ -9795,7 +10750,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
